--- a/public/downloads/원가분석_템플릿.xlsx
+++ b/public/downloads/원가분석_템플릿.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="216">
-  <si>
-    <t>📘 우리 매장 · 메뉴 원가 분석서</t>
-  </si>
-  <si>
-    <t>원가 분석 템플릿 · 예시 데이터가 들어 있습니다 · v1.0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="232">
+  <si>
+    <t>📘 우리 매장 · 레시피 · 원가 관리</t>
+  </si>
+  <si>
+    <t>예시 데이터가 들어 있습니다 — 지우고 우리 가게 것으로 채우세요 · v2.0</t>
   </si>
   <si>
     <t>▸  이 파일의 구조</t>
@@ -110,10 +110,10 @@
     <t>▸  계산 방식</t>
   </si>
   <si>
-    <t>g당 단가</t>
-  </si>
-  <si>
-    <t>구매가격 ÷ 총중량(g)</t>
+    <t>단가</t>
+  </si>
+  <si>
+    <t>무게 품목: 구매가격 ÷ 총중량(g) → 원/g   ·   개수 품목: 구매가격 ÷ 규격수량 → 원/개</t>
   </si>
   <si>
     <t>재료비</t>
@@ -185,6 +185,15 @@
     <t>같은 데이터로 만든 웹 버전에서는 PC·휴대폰 모두에서 단가를 수정하고 이 엑셀을 다시 내려받을 수 있습니다.</t>
   </si>
   <si>
+    <t>▸  오픈소스 라이선스 고지</t>
+  </si>
+  <si>
+    <t>ExcelJS (MIT)</t>
+  </si>
+  <si>
+    <t>Copyright (c) 2014-2019 Guyon Roche · https://github.com/exceljs/exceljs — 이 파일을 만드는 데 사용되었습니다. MIT 라이선스 전문은 함께 제공되는 THIRD-PARTY-NOTICES 문서를 참고하세요.</t>
+  </si>
+  <si>
     <t>① ~ ⑤ 시트의 값이 바뀌면 이 시트도 함께 자동으로 갱신됩니다.</t>
   </si>
   <si>
@@ -245,6 +254,9 @@
     <t>🥗 사이드</t>
   </si>
   <si>
+    <t>🥤 음료</t>
+  </si>
+  <si>
     <t>🍽 세트메뉴</t>
   </si>
   <si>
@@ -263,7 +275,7 @@
     <t>원가율 하위 10 (효자 메뉴)</t>
   </si>
   <si>
-    <t>메뉴 3개 전체. 판매가(노란 셀)만 고치면 원가율·마진이 즉시 다시 계산됩니다.</t>
+    <t>메뉴 4개 전체. 판매가(노란 셀)만 고치면 원가율·마진이 즉시 다시 계산됩니다.</t>
   </si>
   <si>
     <t>💡  공급가액 = 판매가 ÷ 부가세 계수 (③ 시트).  원가율·마진은 모두 공급가액 기준입니다.  고정비 배분 = 공급가액 × 고정비 배분율.  총원가 = 식재료원가 + 고정비 배분.</t>
@@ -297,6 +309,9 @@
     <t>감자 크림 수프</t>
   </si>
   <si>
+    <t>콜라</t>
+  </si>
+  <si>
     <t>런치 세트</t>
   </si>
   <si>
@@ -417,19 +432,25 @@
     <t>수돗물 — 원가 0원 처리</t>
   </si>
   <si>
+    <t>콜라 (355ml 캔)</t>
+  </si>
+  <si>
+    <t>개</t>
+  </si>
+  <si>
+    <t>개수로 계산되는 예시입니다</t>
+  </si>
+  <si>
     <t>메뉴</t>
   </si>
   <si>
-    <t>개</t>
-  </si>
-  <si>
     <t>단품 원가를 그대로 가져옵니다</t>
   </si>
   <si>
-    <t>노란 셀(구매가격·규격)만 수정하세요. g당 단가와 전체 메뉴 원가가 자동으로 다시 계산됩니다.</t>
-  </si>
-  <si>
-    <t>💡  g당 단가 = 구매가격 ÷ 총중량(g).  총중량이 0이면 0원으로 처리되어 오류가 나지 않습니다(개당 판매 품목 등).</t>
+    <t>노란 셀(구매가격·규격)만 수정하세요. 단가와 전체 메뉴 원가가 자동으로 다시 계산됩니다.</t>
+  </si>
+  <si>
+    <t>💡  무게로 사는 것은 단가 = 구매가격 ÷ 총중량(g).  캔·포장용기처럼 개수로 사는 것은 단가 = 구매가격 ÷ 규격수량(원/개).</t>
   </si>
   <si>
     <t>식재료명</t>
@@ -444,6 +465,9 @@
     <t>총중량(g)</t>
   </si>
   <si>
+    <t>단가 (원/g·원/개)</t>
+  </si>
+  <si>
     <t>kg</t>
   </si>
   <si>
@@ -453,6 +477,12 @@
     <t>간장</t>
   </si>
   <si>
+    <t>개수 단위 (원/개)</t>
+  </si>
+  <si>
+    <t>배달 용기 (중)</t>
+  </si>
+  <si>
     <t>② 프렙(반제품) 원가</t>
   </si>
   <si>
@@ -621,34 +651,46 @@
     <t>-</t>
   </si>
   <si>
-    <t>① 회사 이름 바꾸기</t>
-  </si>
-  <si>
-    <t>[고정비] 화면 맨 아래 「기본 정보」에서 회사·매장 이름을 입력하세요. 화면과 엑셀 제목에 반영됩니다.</t>
-  </si>
-  <si>
-    <t>② 식재료 등록</t>
-  </si>
-  <si>
-    <t>[식재료] 화면에서 「＋ 식재료 추가」로 우리 매장이 쓰는 재료와 구매가격·규격을 넣으세요.</t>
-  </si>
-  <si>
-    <t>③ 고정비 입력</t>
-  </si>
-  <si>
-    <t>[고정비] 화면에서 우리 매장의 월 고정비와 월 추정매출을 실제 값으로 바꾸세요.</t>
-  </si>
-  <si>
-    <t>④ 메뉴 등록</t>
-  </si>
-  <si>
-    <t>[메뉴] 화면 아래 입력칸에 메뉴 이름·카테고리·판매가를 넣고 「＋ 메뉴 추가」를 누르면 상세가 열립니다.</t>
-  </si>
-  <si>
-    <t>⑤ 예시 데이터 정리</t>
-  </si>
-  <si>
-    <t>치킨 볶음밥 · 감자 크림 수프 · 런치 세트는 사용법을 보여주기 위한 예시입니다. 다 익히셨으면 지우세요.</t>
+    <t>① 관리자 로그인 등록</t>
+  </si>
+  <si>
+    <t>화면 위 🔒 을 눌러 원하는 아이디·비밀번호를 정하세요. 등록 전에는 아무 값으로나 로그인되니, 직원에게 파일을 주기 전에 먼저 등록해 두세요.</t>
+  </si>
+  <si>
+    <t>② 가게 이름 바꾸기</t>
+  </si>
+  <si>
+    <t>[고정비] 화면 맨 아래 「기본 정보」에서 가게 이름을 입력하세요. 화면과 엑셀 제목에 반영됩니다.</t>
+  </si>
+  <si>
+    <t>③ 식재료 등록</t>
+  </si>
+  <si>
+    <t>[식재료] 화면에서 사 오는 재료와 구매가격·규격을 넣으세요. 엑셀을 쓰고 계시면 「📋 엑셀에서 일괄 등록」으로 한 번에 넣을 수 있습니다.</t>
+  </si>
+  <si>
+    <t>④ 고정비·월매출 입력</t>
+  </si>
+  <si>
+    <t>[고정비] 화면에서 인건비·임대료와 월 추정매출을 우리 가게 값으로 바꾸세요. 이 둘로 메뉴마다 붙는 고정비가 정해집니다.</t>
+  </si>
+  <si>
+    <t>⑤ 메뉴와 레시피 등록</t>
+  </si>
+  <si>
+    <t>[메뉴] 화면에서 메뉴를 추가하고, 메뉴를 눌러 재료·조리법·사진을 채우세요. 주방 화면에 그대로 나갑니다.</t>
+  </si>
+  <si>
+    <t>⑥ 배달하신다면 포장용기를 꼭 넣으세요</t>
+  </si>
+  <si>
+    <t>포장용기·수저·비닐봉투는 개수로 사는 품목이라 빠뜨리기 쉽습니다. [식재료]에 「개수」 단위로 등록한 뒤 배달 메뉴에 재료로 넣으면 원가에 반영됩니다. 예시로 「배달 용기 (중)」을 넣어 두었습니다.</t>
+  </si>
+  <si>
+    <t>⑦ 예시 데이터 정리</t>
+  </si>
+  <si>
+    <t>치킨 볶음밥 · 감자 크림 수프 · 콜라 · 런치 세트는 사용법을 보여주기 위한 예시입니다. 다 익히셨으면 지우세요.</t>
   </si>
   <si>
     <t>예시 데이터</t>
@@ -657,13 +699,19 @@
     <t>식재료 + 프렙 사용 예시</t>
   </si>
   <si>
-    <t>일반 식재료와 미리 만들어 둔 프렙(반제품)을 함께 쓰는 메뉴의 예시입니다.</t>
+    <t>일반 식재료와 미리 만들어 둔 프렙(반제품)을 함께 쓰는 메뉴입니다. 수율 90%도 함께 보여줍니다.</t>
   </si>
   <si>
     <t>수율 · 무료 항목 예시</t>
   </si>
   <si>
     <t>껍질을 벗겨 버리는 손실(수율 85%)과 원가가 들지 않는 수돗물(무료) 처리 예시입니다.</t>
+  </si>
+  <si>
+    <t>개수 단위 예시</t>
+  </si>
+  <si>
+    <t>캔·병·포장용기처럼 무게가 아니라 개수로 사는 품목의 원가 계산 예시입니다. 24개 21,000원 → 1개 875원.</t>
   </si>
   <si>
     <t>세트메뉴 예시</t>
@@ -1169,7 +1217,7 @@
     <xf numFmtId="0" fontId="29" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1567,7 +1615,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1816,14 +1864,31 @@
         <v>53</v>
       </c>
     </row>
+    <row r="36" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1835,7 +1900,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1867,7 +1932,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1882,41 +1947,41 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K4" s="15"/>
     </row>
     <row r="5" ht="38" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="16">
-        <f>COUNTA('④ 메뉴 원가표'!$C$6:$C$8)</f>
+        <f>COUNTA('④ 메뉴 원가표'!$C$6:$C$9)</f>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="17">
-        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,'④ 메뉴 원가표'!$F$9/'④ 메뉴 원가표'!$E$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$10&gt;0,'④ 메뉴 원가표'!$F$10/'④ 메뉴 원가표'!$E$10,0)</f>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17">
-        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,'④ 메뉴 원가표'!$I$9/'④ 메뉴 원가표'!$E$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$10&gt;0,'④ 메뉴 원가표'!$I$10/'④ 메뉴 원가표'!$E$10,0)</f>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
-        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,('④ 메뉴 원가표'!$E$9-'④ 메뉴 원가표'!$I$9)/'④ 메뉴 원가표'!$E$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$10&gt;0,('④ 메뉴 원가표'!$E$10-'④ 메뉴 원가표'!$I$10)/'④ 메뉴 원가표'!$E$10,0)</f>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17">
@@ -1926,7 +1991,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1945,10 +2010,10 @@
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="19">
-        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*양호*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$9,"*양호*")</f>
       </c>
       <c r="E8" s="20">
-        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D8/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
+        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$9)&gt;0,D8/COUNTA('④ 메뉴 원가표'!$C$6:$C$9),0)</f>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -1957,10 +2022,10 @@
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="22">
-        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*주의*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$9,"*주의*")</f>
       </c>
       <c r="E9" s="23">
-        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D9/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
+        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$9)&gt;0,D9/COUNTA('④ 메뉴 원가표'!$C$6:$C$9),0)</f>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -1969,27 +2034,27 @@
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="25">
-        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*과다*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$9,"*과다*")</f>
       </c>
       <c r="E10" s="26">
-        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D10/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
+        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$9)&gt;0,D10/COUNTA('④ 메뉴 원가표'!$C$6:$C$9),0)</f>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="28">
-        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*판매가*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$9,"*판매가*")</f>
       </c>
       <c r="E11" s="29">
-        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D11/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
+        <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$9)&gt;0,D11/COUNTA('④ 메뉴 원가표'!$C$6:$C$9),0)</f>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2004,63 +2069,63 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E14" s="30" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15" s="32">
-        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리")</f>
       </c>
       <c r="D15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$D$6:$D$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리",'④ 메뉴 원가표'!$D$6:$D$9)</f>
       </c>
       <c r="E15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$E$6:$E$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리",'④ 메뉴 원가표'!$E$6:$E$9)</f>
       </c>
       <c r="F15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리",'④ 메뉴 원가표'!$F$6:$F$9)</f>
       </c>
       <c r="G15" s="34">
         <f>IF(E15&gt;0,F15/E15,"")</f>
       </c>
       <c r="H15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$H$6:$H$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리",'④ 메뉴 원가표'!$H$6:$H$9)</f>
       </c>
       <c r="I15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$I$6:$I$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍳 메인 요리",'④ 메뉴 원가표'!$I$6:$I$9)</f>
       </c>
       <c r="J15" s="35">
         <f>IF(E15&gt;0,(E15-I15)/E15,"")</f>
@@ -2068,28 +2133,28 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C16" s="37">
-        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드")</f>
       </c>
       <c r="D16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$D$6:$D$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드",'④ 메뉴 원가표'!$D$6:$D$9)</f>
       </c>
       <c r="E16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$E$6:$E$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드",'④ 메뉴 원가표'!$E$6:$E$9)</f>
       </c>
       <c r="F16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드",'④ 메뉴 원가표'!$F$6:$F$9)</f>
       </c>
       <c r="G16" s="39">
         <f>IF(E16&gt;0,F16/E16,"")</f>
       </c>
       <c r="H16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$H$6:$H$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드",'④ 메뉴 원가표'!$H$6:$H$9)</f>
       </c>
       <c r="I16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$I$6:$I$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥗 사이드",'④ 메뉴 원가표'!$I$6:$I$9)</f>
       </c>
       <c r="J16" s="40">
         <f>IF(E16&gt;0,(E16-I16)/E16,"")</f>
@@ -2097,367 +2162,396 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C17" s="32">
-        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료")</f>
       </c>
       <c r="D17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$D$6:$D$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료",'④ 메뉴 원가표'!$D$6:$D$9)</f>
       </c>
       <c r="E17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$E$6:$E$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료",'④ 메뉴 원가표'!$E$6:$E$9)</f>
       </c>
       <c r="F17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료",'④ 메뉴 원가표'!$F$6:$F$9)</f>
       </c>
       <c r="G17" s="34">
         <f>IF(E17&gt;0,F17/E17,"")</f>
       </c>
       <c r="H17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$H$6:$H$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료",'④ 메뉴 원가표'!$H$6:$H$9)</f>
       </c>
       <c r="I17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$I$6:$I$8)</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🥤 음료",'④ 메뉴 원가표'!$I$6:$I$9)</f>
       </c>
       <c r="J17" s="35">
         <f>IF(E17&gt;0,(E17-I17)/E17,"")</f>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-    </row>
-    <row r="20" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="30" t="s">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="42" t="s">
+      <c r="C18" s="37">
+        <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴")</f>
+      </c>
+      <c r="D18" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴",'④ 메뉴 원가표'!$D$6:$D$9)</f>
+      </c>
+      <c r="E18" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴",'④ 메뉴 원가표'!$E$6:$E$9)</f>
+      </c>
+      <c r="F18" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴",'④ 메뉴 원가표'!$F$6:$F$9)</f>
+      </c>
+      <c r="G18" s="39">
+        <f>IF(E18&gt;0,F18/E18,"")</f>
+      </c>
+      <c r="H18" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴",'④ 메뉴 원가표'!$H$6:$H$9)</f>
+      </c>
+      <c r="I18" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$9,"🍽 세트메뉴",'④ 메뉴 원가표'!$I$6:$I$9)</f>
+      </c>
+      <c r="J18" s="40">
+        <f>IF(E18&gt;0,(E18-I18)/E18,"")</f>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="43">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="43">
         <v>1</v>
       </c>
-      <c r="C21" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D21" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E21" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F21" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="43">
+      <c r="C22" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D22" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E22" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F22" s="45">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="43">
         <v>1</v>
       </c>
-      <c r="I21" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J21" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="48">
+      <c r="I22" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J22" s="47">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,1),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="48">
         <v>2</v>
       </c>
-      <c r="C22" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D22" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E22" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F22" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="48">
+      <c r="C23" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D23" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E23" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F23" s="50">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="48">
         <v>2</v>
       </c>
-      <c r="I22" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J22" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="43">
+      <c r="I23" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J23" s="51">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,2),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="43">
         <v>3</v>
       </c>
-      <c r="C23" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D23" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E23" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F23" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="43">
+      <c r="C24" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D24" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E24" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F24" s="45">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="43">
         <v>3</v>
       </c>
-      <c r="I23" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J23" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="48">
+      <c r="I24" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J24" s="47">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,3),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="48">
         <v>4</v>
       </c>
-      <c r="C24" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D24" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E24" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F24" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="48">
+      <c r="C25" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D25" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E25" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F25" s="50">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="48">
         <v>4</v>
       </c>
-      <c r="I24" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J24" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="43">
+      <c r="I25" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J25" s="51">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,4),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="43">
         <v>5</v>
       </c>
-      <c r="C25" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D25" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E25" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F25" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G25" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="43">
+      <c r="C26" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D26" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E26" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F26" s="45">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="43">
         <v>5</v>
       </c>
-      <c r="I25" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J25" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="48">
+      <c r="I26" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J26" s="47">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,5),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="48">
         <v>6</v>
       </c>
-      <c r="C26" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D26" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E26" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F26" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="48">
+      <c r="C27" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D27" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E27" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F27" s="50">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="48">
         <v>6</v>
       </c>
-      <c r="I26" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J26" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="43">
+      <c r="I27" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J27" s="51">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,6),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="43">
         <v>7</v>
       </c>
-      <c r="C27" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D27" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E27" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F27" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G27" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="43">
+      <c r="C28" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D28" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E28" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F28" s="45">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="43">
         <v>7</v>
       </c>
-      <c r="I27" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J27" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="48">
+      <c r="I28" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J28" s="47">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,7),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="48">
         <v>8</v>
       </c>
-      <c r="C28" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D28" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E28" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F28" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="48">
+      <c r="C29" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D29" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E29" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F29" s="50">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G29" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="48">
         <v>8</v>
       </c>
-      <c r="I28" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J28" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="43">
+      <c r="I29" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J29" s="51">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,8),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="43">
         <v>9</v>
       </c>
-      <c r="C29" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D29" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E29" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F29" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G29" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H29" s="43">
+      <c r="C30" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D30" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E30" s="33">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F30" s="45">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="43">
         <v>9</v>
       </c>
-      <c r="I29" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J29" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="48">
+      <c r="I30" s="44">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J30" s="47">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,9),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="48">
         <v>10</v>
       </c>
-      <c r="C30" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="D30" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="E30" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="F30" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="G30" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" s="48">
+      <c r="C31" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="D31" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="E31" s="38">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="F31" s="50">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="G31" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="48">
         <v>10</v>
       </c>
-      <c r="I30" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
-      </c>
-      <c r="J30" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
+      <c r="I31" s="49">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
+      </c>
+      <c r="J31" s="51">
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$9,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$9,10),'④ 메뉴 원가표'!$N$6:$N$9,0)),"")</f>
       </c>
     </row>
   </sheetData>
@@ -2480,10 +2574,10 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
-  <conditionalFormatting sqref="G15:G17">
+  <conditionalFormatting sqref="G15:G18">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2505,7 +2599,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2541,7 +2635,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2559,7 +2653,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -2577,46 +2671,46 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N5" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2624,10 +2718,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D6" s="55">
         <v>9000</v>
@@ -2636,7 +2730,7 @@
         <f>ROUND($D6/'③ 고정비 설정'!$C$17,0)</f>
       </c>
       <c r="F6" s="57">
-        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$20,$C6,'⑤ 레시피 상세'!$K$6:$K$20),1)</f>
+        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$21,$C6,'⑤ 레시피 상세'!$K$6:$K$21),1)</f>
       </c>
       <c r="G6" s="58">
         <f>IF($E6&gt;0,$F6/$E6,"")</f>
@@ -2668,10 +2762,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D7" s="55">
         <v>5000</v>
@@ -2680,7 +2774,7 @@
         <f>ROUND($D7/'③ 고정비 설정'!$C$17,0)</f>
       </c>
       <c r="F7" s="57">
-        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$20,$C7,'⑤ 레시피 상세'!$K$6:$K$20),1)</f>
+        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$21,$C7,'⑤ 레시피 상세'!$K$6:$K$21),1)</f>
       </c>
       <c r="G7" s="58">
         <f>IF($E7&gt;0,$F7/$E7,"")</f>
@@ -2712,19 +2806,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D8" s="55">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="E8" s="56">
         <f>ROUND($D8/'③ 고정비 설정'!$C$17,0)</f>
       </c>
       <c r="F8" s="57">
-        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$21:$B$22,$C8,'⑤ 레시피 상세'!$K$21:$K$22),1)</f>
+        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$21,$C8,'⑤ 레시피 상세'!$K$6:$K$21),1)</f>
       </c>
       <c r="G8" s="58">
         <f>IF($E8&gt;0,$F8/$E8,"")</f>
@@ -2752,52 +2846,96 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="66">
-        <f>SUM(D6:D8)</f>
-      </c>
-      <c r="E9" s="66">
-        <f>SUM(E6:E8)</f>
-      </c>
-      <c r="F9" s="66">
-        <f>SUM(F6:F8)</f>
-      </c>
-      <c r="G9" s="67">
-        <f>IF(E9&gt;0,F9/E9,"")</f>
-      </c>
-      <c r="H9" s="66">
-        <f>SUM(H6:H8)</f>
-      </c>
-      <c r="I9" s="66">
-        <f>SUM(I6:I8)</f>
-      </c>
-      <c r="J9" s="67">
-        <f>IF(E9&gt;0,I9/E9,"")</f>
-      </c>
-      <c r="K9" s="66">
-        <f>IF(E9&gt;0,E9-I9,"")</f>
-      </c>
-      <c r="L9" s="67">
-        <f>IF(E9&gt;0,K9/E9,"")</f>
-      </c>
-      <c r="M9" s="68">
-        <f>"✅"&amp;COUNTIF(M6:M8,"*양호*")&amp;"  🟡"&amp;COUNTIF(M6:M8,"*주의*")&amp;"  🔴"&amp;COUNTIF(M6:M8,"*과다*")</f>
-      </c>
-      <c r="N9" s="69"/>
+      <c r="A9" s="63">
+        <v>4</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="55">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="56">
+        <f>ROUND($D9/'③ 고정비 설정'!$C$17,0)</f>
+      </c>
+      <c r="F9" s="57">
+        <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$22:$B$23,$C9,'⑤ 레시피 상세'!$K$22:$K$23),1)</f>
+      </c>
+      <c r="G9" s="58">
+        <f>IF($E9&gt;0,$F9/$E9,"")</f>
+      </c>
+      <c r="H9" s="57">
+        <f>ROUND($E9*'③ 고정비 설정'!$C$20,0)</f>
+      </c>
+      <c r="I9" s="57">
+        <f>ROUND($F9+$H9,0)</f>
+      </c>
+      <c r="J9" s="59">
+        <f>IF($E9&gt;0,$I9/$E9,"")</f>
+      </c>
+      <c r="K9" s="57">
+        <f>IF($E9&gt;0,$E9-$I9,"")</f>
+      </c>
+      <c r="L9" s="60">
+        <f>IF($E9&gt;0,$K9/$E9,"")</f>
+      </c>
+      <c r="M9" s="61">
+        <f>IF($D9&lt;=0,"⬜ 판매가 입력",IF($F9&lt;=0,"⬜ 재료 확인",IF($G9&lt;='③ 고정비 설정'!$C$21,"✅ 양호",IF($G9&lt;='③ 고정비 설정'!$C$22,"🟡 주의","🔴 과다"))))</f>
+      </c>
+      <c r="N9" s="62">
+        <f>IF($D9&gt;0,$G9+ROW()/1000000,"")</f>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66">
+        <f>SUM(D6:D9)</f>
+      </c>
+      <c r="E10" s="66">
+        <f>SUM(E6:E9)</f>
+      </c>
+      <c r="F10" s="66">
+        <f>SUM(F6:F9)</f>
+      </c>
+      <c r="G10" s="67">
+        <f>IF(E10&gt;0,F10/E10,"")</f>
+      </c>
+      <c r="H10" s="66">
+        <f>SUM(H6:H9)</f>
+      </c>
+      <c r="I10" s="66">
+        <f>SUM(I6:I9)</f>
+      </c>
+      <c r="J10" s="67">
+        <f>IF(E10&gt;0,I10/E10,"")</f>
+      </c>
+      <c r="K10" s="66">
+        <f>IF(E10&gt;0,E10-I10,"")</f>
+      </c>
+      <c r="L10" s="67">
+        <f>IF(E10&gt;0,K10/E10,"")</f>
+      </c>
+      <c r="M10" s="68">
+        <f>"✅"&amp;COUNTIF(M6:M9,"*양호*")&amp;"  🟡"&amp;COUNTIF(M6:M9,"*주의*")&amp;"  🔴"&amp;COUNTIF(M6:M9,"*과다*")</f>
+      </c>
+      <c r="N10" s="69"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M8"/>
+  <autoFilter ref="A5:M9"/>
   <mergeCells count="4">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:G8">
+  <conditionalFormatting sqref="G6:G9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>'③ 고정비 설정'!$C$22</formula>
     </cfRule>
@@ -2808,7 +2946,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L8">
+  <conditionalFormatting sqref="L6:L9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2830,7 +2968,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2846,7 +2984,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2862,7 +3000,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2878,7 +3016,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -2894,700 +3032,738 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="53">
         <v>1</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6" s="72">
         <v>200</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I6" s="73">
         <v>1</v>
       </c>
       <c r="J6" s="74">
-        <f>IF($D6="무료",0,IF($D6="메뉴",0,IF($D6="프렙",IFERROR(VLOOKUP($E6,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E6,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D6="무료",0,IF($D6="메뉴",0,IF($D6="프렙",IFERROR(VLOOKUP($E6,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E6,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K6" s="75">
         <f>IF($D6="메뉴",ROUND($G6*$J6,1),IF($I6&gt;0,ROUND($G6/$I6*$J6,1),0))</f>
       </c>
       <c r="L6" s="54" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" s="53">
         <v>2</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7" s="72">
         <v>100</v>
       </c>
       <c r="H7" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I7" s="73">
         <v>0.9</v>
       </c>
       <c r="J7" s="74">
-        <f>IF($D7="무료",0,IF($D7="메뉴",0,IF($D7="프렙",IFERROR(VLOOKUP($E7,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E7,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D7="무료",0,IF($D7="메뉴",0,IF($D7="프렙",IFERROR(VLOOKUP($E7,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E7,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K7" s="75">
         <f>IF($D7="메뉴",ROUND($G7*$J7,1),IF($I7&gt;0,ROUND($G7/$I7*$J7,1),0))</f>
       </c>
       <c r="L7" s="54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" s="53">
         <v>3</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" s="72">
         <v>30</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I8" s="73">
         <v>1</v>
       </c>
       <c r="J8" s="74">
-        <f>IF($D8="무료",0,IF($D8="메뉴",0,IF($D8="프렙",IFERROR(VLOOKUP($E8,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E8,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D8="무료",0,IF($D8="메뉴",0,IF($D8="프렙",IFERROR(VLOOKUP($E8,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E8,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K8" s="75">
         <f>IF($D8="메뉴",ROUND($G8*$J8,1),IF($I8&gt;0,ROUND($G8/$I8*$J8,1),0))</f>
       </c>
       <c r="L8" s="54" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" s="53">
         <v>4</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G9" s="72">
         <v>20</v>
       </c>
       <c r="H9" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I9" s="73">
         <v>1</v>
       </c>
       <c r="J9" s="74">
-        <f>IF($D9="무료",0,IF($D9="메뉴",0,IF($D9="프렙",IFERROR(VLOOKUP($E9,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E9,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D9="무료",0,IF($D9="메뉴",0,IF($D9="프렙",IFERROR(VLOOKUP($E9,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E9,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K9" s="75">
         <f>IF($D9="메뉴",ROUND($G9*$J9,1),IF($I9&gt;0,ROUND($G9/$I9*$J9,1),0))</f>
       </c>
       <c r="L9" s="54" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" s="53">
         <v>5</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G10" s="72">
         <v>15</v>
       </c>
       <c r="H10" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I10" s="73">
         <v>1</v>
       </c>
       <c r="J10" s="74">
-        <f>IF($D10="무료",0,IF($D10="메뉴",0,IF($D10="프렙",IFERROR(VLOOKUP($E10,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E10,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D10="무료",0,IF($D10="메뉴",0,IF($D10="프렙",IFERROR(VLOOKUP($E10,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E10,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K10" s="75">
         <f>IF($D10="메뉴",ROUND($G10*$J10,1),IF($I10&gt;0,ROUND($G10/$I10*$J10,1),0))</f>
       </c>
       <c r="L10" s="54" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" s="53">
         <v>6</v>
       </c>
       <c r="D11" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F11" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G11" s="72">
         <v>3</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I11" s="73">
         <v>1</v>
       </c>
       <c r="J11" s="74">
-        <f>IF($D11="무료",0,IF($D11="메뉴",0,IF($D11="프렙",IFERROR(VLOOKUP($E11,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E11,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D11="무료",0,IF($D11="메뉴",0,IF($D11="프렙",IFERROR(VLOOKUP($E11,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E11,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K11" s="75">
         <f>IF($D11="메뉴",ROUND($G11*$J11,1),IF($I11&gt;0,ROUND($G11/$I11*$J11,1),0))</f>
       </c>
       <c r="L11" s="54" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" s="53">
         <v>7</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F12" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12" s="72">
         <v>1</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I12" s="73">
         <v>1</v>
       </c>
       <c r="J12" s="74">
-        <f>IF($D12="무료",0,IF($D12="메뉴",0,IF($D12="프렙",IFERROR(VLOOKUP($E12,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E12,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D12="무료",0,IF($D12="메뉴",0,IF($D12="프렙",IFERROR(VLOOKUP($E12,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E12,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K12" s="75">
         <f>IF($D12="메뉴",ROUND($G12*$J12,1),IF($I12&gt;0,ROUND($G12/$I12*$J12,1),0))</f>
       </c>
       <c r="L12" s="54" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" s="53">
         <v>8</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F13" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G13" s="72">
         <v>10</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I13" s="73">
         <v>1</v>
       </c>
       <c r="J13" s="74">
-        <f>IF($D13="무료",0,IF($D13="메뉴",0,IF($D13="프렙",IFERROR(VLOOKUP($E13,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E13,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D13="무료",0,IF($D13="메뉴",0,IF($D13="프렙",IFERROR(VLOOKUP($E13,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E13,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K13" s="75">
         <f>IF($D13="메뉴",ROUND($G13*$J13,1),IF($I13&gt;0,ROUND($G13/$I13*$J13,1),0))</f>
       </c>
       <c r="L13" s="54" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" s="53">
         <v>9</v>
       </c>
       <c r="D14" s="76" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F14" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G14" s="72">
         <v>40</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I14" s="73">
         <v>1</v>
       </c>
       <c r="J14" s="74">
-        <f>IF($D14="무료",0,IF($D14="메뉴",0,IF($D14="프렙",IFERROR(VLOOKUP($E14,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E14,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D14="무료",0,IF($D14="메뉴",0,IF($D14="프렙",IFERROR(VLOOKUP($E14,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E14,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K14" s="75">
         <f>IF($D14="메뉴",ROUND($G14*$J14,1),IF($I14&gt;0,ROUND($G14/$I14*$J14,1),0))</f>
       </c>
       <c r="L14" s="54" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C15" s="63">
         <v>1</v>
       </c>
       <c r="D15" s="78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G15" s="72">
         <v>150</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I15" s="73">
         <v>0.85</v>
       </c>
       <c r="J15" s="74">
-        <f>IF($D15="무료",0,IF($D15="메뉴",0,IF($D15="프렙",IFERROR(VLOOKUP($E15,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E15,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D15="무료",0,IF($D15="메뉴",0,IF($D15="프렙",IFERROR(VLOOKUP($E15,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E15,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K15" s="75">
         <f>IF($D15="메뉴",ROUND($G15*$J15,1),IF($I15&gt;0,ROUND($G15/$I15*$J15,1),0))</f>
       </c>
       <c r="L15" s="64" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" s="63">
         <v>2</v>
       </c>
       <c r="D16" s="78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G16" s="72">
         <v>30</v>
       </c>
       <c r="H16" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I16" s="73">
         <v>1</v>
       </c>
       <c r="J16" s="74">
-        <f>IF($D16="무료",0,IF($D16="메뉴",0,IF($D16="프렙",IFERROR(VLOOKUP($E16,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E16,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D16="무료",0,IF($D16="메뉴",0,IF($D16="프렙",IFERROR(VLOOKUP($E16,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E16,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K16" s="75">
         <f>IF($D16="메뉴",ROUND($G16*$J16,1),IF($I16&gt;0,ROUND($G16/$I16*$J16,1),0))</f>
       </c>
       <c r="L16" s="64" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C17" s="63">
         <v>3</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G17" s="72">
         <v>120</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I17" s="73">
         <v>1</v>
       </c>
       <c r="J17" s="74">
-        <f>IF($D17="무료",0,IF($D17="메뉴",0,IF($D17="프렙",IFERROR(VLOOKUP($E17,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E17,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D17="무료",0,IF($D17="메뉴",0,IF($D17="프렙",IFERROR(VLOOKUP($E17,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E17,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K17" s="75">
         <f>IF($D17="메뉴",ROUND($G17*$J17,1),IF($I17&gt;0,ROUND($G17/$I17*$J17,1),0))</f>
       </c>
       <c r="L17" s="64" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C18" s="63">
         <v>4</v>
       </c>
       <c r="D18" s="78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F18" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G18" s="72">
         <v>10</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I18" s="73">
         <v>1</v>
       </c>
       <c r="J18" s="74">
-        <f>IF($D18="무료",0,IF($D18="메뉴",0,IF($D18="프렙",IFERROR(VLOOKUP($E18,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E18,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D18="무료",0,IF($D18="메뉴",0,IF($D18="프렙",IFERROR(VLOOKUP($E18,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E18,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K18" s="75">
         <f>IF($D18="메뉴",ROUND($G18*$J18,1),IF($I18&gt;0,ROUND($G18/$I18*$J18,1),0))</f>
       </c>
       <c r="L18" s="64" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C19" s="63">
         <v>5</v>
       </c>
       <c r="D19" s="78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G19" s="72">
         <v>3</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I19" s="73">
         <v>1</v>
       </c>
       <c r="J19" s="74">
-        <f>IF($D19="무료",0,IF($D19="메뉴",0,IF($D19="프렙",IFERROR(VLOOKUP($E19,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E19,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D19="무료",0,IF($D19="메뉴",0,IF($D19="프렙",IFERROR(VLOOKUP($E19,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E19,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K19" s="75">
         <f>IF($D19="메뉴",ROUND($G19*$J19,1),IF($I19&gt;0,ROUND($G19/$I19*$J19,1),0))</f>
       </c>
       <c r="L19" s="64" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C20" s="63">
         <v>6</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G20" s="72">
         <v>100</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I20" s="73">
         <v>1</v>
       </c>
       <c r="J20" s="74">
-        <f>IF($D20="무료",0,IF($D20="메뉴",0,IF($D20="프렙",IFERROR(VLOOKUP($E20,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E20,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D20="무료",0,IF($D20="메뉴",0,IF($D20="프렙",IFERROR(VLOOKUP($E20,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E20,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K20" s="75">
         <f>IF($D20="메뉴",ROUND($G20*$J20,1),IF($I20&gt;0,ROUND($G20/$I20*$J20,1),0))</f>
       </c>
       <c r="L20" s="64" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="70" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C21" s="53">
         <v>1</v>
       </c>
-      <c r="D21" s="80" t="s">
-        <v>131</v>
+      <c r="D21" s="71" t="s">
+        <v>111</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="F21" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G21" s="72">
         <v>1</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I21" s="73">
         <v>1</v>
       </c>
       <c r="J21" s="74">
-        <f>IF($D21="무료",0,IF($D21="메뉴",IFERROR(VLOOKUP($E21,'④ 메뉴 원가표'!$C$6:$F$7,4,FALSE),0),IF($D21="프렙",IFERROR(VLOOKUP($E21,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E21,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D21="무료",0,IF($D21="메뉴",0,IF($D21="프렙",IFERROR(VLOOKUP($E21,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E21,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K21" s="75">
         <f>IF($D21="메뉴",ROUND($G21*$J21,1),IF($I21&gt;0,ROUND($G21/$I21*$J21,1),0))</f>
       </c>
       <c r="L21" s="54" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="53">
-        <v>2</v>
+      <c r="A22" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="63">
+        <v>1</v>
       </c>
       <c r="D22" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="70" t="s">
-        <v>63</v>
+        <v>139</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>66</v>
       </c>
       <c r="G22" s="72">
         <v>1</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>132</v>
+      <c r="H22" s="63" t="s">
+        <v>137</v>
       </c>
       <c r="I22" s="73">
         <v>1</v>
       </c>
       <c r="J22" s="74">
-        <f>IF($D22="무료",0,IF($D22="메뉴",IFERROR(VLOOKUP($E22,'④ 메뉴 원가표'!$C$6:$F$7,4,FALSE),0),IF($D22="프렙",IFERROR(VLOOKUP($E22,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E22,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+        <f>IF($D22="무료",0,IF($D22="메뉴",IFERROR(VLOOKUP($E22,'④ 메뉴 원가표'!$C$6:$F$8,4,FALSE),0),IF($D22="프렙",IFERROR(VLOOKUP($E22,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E22,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
       </c>
       <c r="K22" s="75">
         <f>IF($D22="메뉴",ROUND($G22*$J22,1),IF($I22&gt;0,ROUND($G22/$I22*$J22,1),0))</f>
       </c>
-      <c r="L22" s="54" t="s">
-        <v>133</v>
+      <c r="L22" s="64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="63">
+        <v>2</v>
+      </c>
+      <c r="D23" s="80" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="77" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="72">
+        <v>1</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="73">
+        <v>1</v>
+      </c>
+      <c r="J23" s="74">
+        <f>IF($D23="무료",0,IF($D23="메뉴",IFERROR(VLOOKUP($E23,'④ 메뉴 원가표'!$C$6:$F$8,4,FALSE),0),IF($D23="프렙",IFERROR(VLOOKUP($E23,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E23,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0))))</f>
+      </c>
+      <c r="K23" s="75">
+        <f>IF($D23="메뉴",ROUND($G23*$J23,1),IF($I23&gt;0,ROUND($G23/$I23*$J23,1),0))</f>
+      </c>
+      <c r="L23" s="64" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L22"/>
+  <autoFilter ref="A5:L23"/>
   <mergeCells count="3">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="식재료 / 프렙 / 메뉴 / 무료 중에서 선택하세요." sqref="D10:D22">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="식재료 / 프렙 / 메뉴 / 무료 중에서 선택하세요." sqref="D10:D23">
       <formula1>"식재료,프렙,메뉴,무료"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="식재료 / 프렙 / 메뉴 / 무료 중에서 선택하세요." sqref="D6:D22">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="식재료 / 프렙 / 메뉴 / 무료 중에서 선택하세요." sqref="D6:D23">
       <formula1>"식재료,프렙,메뉴,무료"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3601,7 +3777,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3628,7 +3804,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3640,7 +3816,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -3652,28 +3828,28 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3681,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C6" s="55">
         <v>12000</v>
@@ -3690,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F6" s="55">
         <v>1000</v>
@@ -3699,7 +3875,7 @@
         <f>IF(F6&gt;0,C6/F6,0)</f>
       </c>
       <c r="H6" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3707,7 +3883,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C7" s="55">
         <v>62000</v>
@@ -3716,7 +3892,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="63" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F7" s="55">
         <v>20000</v>
@@ -3725,7 +3901,7 @@
         <f>IF(F7&gt;0,C7/F7,0)</f>
       </c>
       <c r="H7" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3733,7 +3909,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C8" s="55">
         <v>14000</v>
@@ -3742,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F8" s="55">
         <v>15000</v>
@@ -3751,7 +3927,7 @@
         <f>IF(F8&gt;0,C8/F8,0)</f>
       </c>
       <c r="H8" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3759,7 +3935,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C9" s="55">
         <v>16500</v>
@@ -3768,7 +3944,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F9" s="55">
         <v>3000</v>
@@ -3777,7 +3953,7 @@
         <f>IF(F9&gt;0,C9/F9,0)</f>
       </c>
       <c r="H9" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3785,7 +3961,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C10" s="55">
         <v>35000</v>
@@ -3794,7 +3970,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F10" s="55">
         <v>20000</v>
@@ -3803,7 +3979,7 @@
         <f>IF(F10&gt;0,C10/F10,0)</f>
       </c>
       <c r="H10" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3811,7 +3987,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C11" s="55">
         <v>1650</v>
@@ -3820,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F11" s="55">
         <v>1000</v>
@@ -3829,7 +4005,7 @@
         <f>IF(F11&gt;0,C11/F11,0)</f>
       </c>
       <c r="H11" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3837,7 +4013,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C12" s="55">
         <v>14500</v>
@@ -3846,7 +4022,7 @@
         <v>13.1</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F12" s="55">
         <v>13100</v>
@@ -3855,7 +4031,7 @@
         <f>IF(F12&gt;0,C12/F12,0)</f>
       </c>
       <c r="H12" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3863,7 +4039,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C13" s="55">
         <v>49500</v>
@@ -3872,7 +4048,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F13" s="55">
         <v>18000</v>
@@ -3881,7 +4057,7 @@
         <f>IF(F13&gt;0,C13/F13,0)</f>
       </c>
       <c r="H13" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3889,7 +4065,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C14" s="55">
         <v>5500</v>
@@ -3898,7 +4074,7 @@
         <v>1.8</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F14" s="55">
         <v>1800</v>
@@ -3907,7 +4083,7 @@
         <f>IF(F14&gt;0,C14/F14,0)</f>
       </c>
       <c r="H14" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3915,7 +4091,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C15" s="55">
         <v>15000</v>
@@ -3924,7 +4100,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F15" s="55">
         <v>15000</v>
@@ -3933,7 +4109,7 @@
         <f>IF(F15&gt;0,C15/F15,0)</f>
       </c>
       <c r="H15" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3941,7 +4117,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C16" s="55">
         <v>9000</v>
@@ -3950,7 +4126,7 @@
         <v>0.4</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F16" s="55">
         <v>400</v>
@@ -3959,7 +4135,7 @@
         <f>IF(F16&gt;0,C16/F16,0)</f>
       </c>
       <c r="H16" s="83" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3967,7 +4143,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C17" s="55">
         <v>4980</v>
@@ -3976,7 +4152,7 @@
         <v>0.5</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F17" s="55">
         <v>500</v>
@@ -3985,11 +4161,63 @@
         <f>IF(F17&gt;0,C17/F17,0)</f>
       </c>
       <c r="H17" s="84" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="53">
+        <v>13</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="55">
+        <v>21000</v>
+      </c>
+      <c r="D18" s="81">
+        <v>24</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="55">
+        <v>0</v>
+      </c>
+      <c r="G18" s="82">
+        <f>IF(D18&gt;0,C18/D18,0)</f>
+      </c>
+      <c r="H18" s="83" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="63">
+        <v>14</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="55">
+        <v>60000</v>
+      </c>
+      <c r="D19" s="81">
+        <v>500</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="55">
+        <v>0</v>
+      </c>
+      <c r="G19" s="82">
+        <f>IF(D19&gt;0,C19/D19,0)</f>
+      </c>
+      <c r="H19" s="84" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H17"/>
+  <autoFilter ref="A5:H19"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4020,7 +4248,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4032,7 +4260,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4044,7 +4272,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -4056,28 +4284,28 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4085,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C6" s="55">
         <v>1200</v>
@@ -4103,12 +4331,12 @@
         <f>SUMIF($A$11:$A$14,$B6,$D$11:$D$14)</f>
       </c>
       <c r="H6" s="44" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4120,45 +4348,45 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D11" s="55">
         <v>1000</v>
       </c>
       <c r="E11" s="74">
-        <f>IFERROR(VLOOKUP($C11,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($C11,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0)</f>
       </c>
       <c r="F11" s="57">
         <f>ROUND($D11*$E11,2)</f>
@@ -4166,19 +4394,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D12" s="55">
         <v>300</v>
       </c>
       <c r="E12" s="74">
-        <f>IFERROR(VLOOKUP($C12,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($C12,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0)</f>
       </c>
       <c r="F12" s="57">
         <f>ROUND($D12*$E12,2)</f>
@@ -4186,19 +4414,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D13" s="55">
         <v>200</v>
       </c>
       <c r="E13" s="74">
-        <f>IFERROR(VLOOKUP($C13,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($C13,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0)</f>
       </c>
       <c r="F13" s="57">
         <f>ROUND($D13*$E13,2)</f>
@@ -4206,19 +4434,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="44" t="s">
         <v>121</v>
-      </c>
-      <c r="B14" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>116</v>
       </c>
       <c r="D14" s="55">
         <v>50</v>
       </c>
       <c r="E14" s="74">
-        <f>IFERROR(VLOOKUP($C14,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($C14,'① 식재료 단가'!$B$6:$G$19,6,FALSE),0)</f>
       </c>
       <c r="F14" s="57">
         <f>ROUND($D14*$E14,2)</f>
@@ -4263,7 +4491,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4272,7 +4500,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -4281,19 +4509,19 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4301,16 +4529,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C6" s="55">
         <v>8000000</v>
       </c>
       <c r="D6" s="85" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4318,16 +4546,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C7" s="55">
         <v>3000000</v>
       </c>
       <c r="D7" s="85" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4335,16 +4563,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C8" s="55">
         <v>800000</v>
       </c>
       <c r="D8" s="85" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4352,16 +4580,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C9" s="55">
         <v>1500000</v>
       </c>
       <c r="D9" s="85" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4369,21 +4597,21 @@
         <v>5</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C10" s="55">
         <v>6000000</v>
       </c>
       <c r="D10" s="85" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E10" s="83" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="86" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B11" s="86"/>
       <c r="C11" s="87">
@@ -4391,12 +4619,12 @@
       </c>
       <c r="D11" s="88"/>
       <c r="E11" s="89" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="86" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B12" s="86"/>
       <c r="C12" s="87">
@@ -4404,12 +4632,12 @@
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="89" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -4418,20 +4646,20 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="90" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B15" s="90"/>
       <c r="C15" s="85" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="54" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="90" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B16" s="90"/>
       <c r="C16" s="73">
@@ -4439,12 +4667,12 @@
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="54" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="90" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B17" s="90"/>
       <c r="C17" s="91">
@@ -4452,12 +4680,12 @@
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="54" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B18" s="90"/>
       <c r="C18" s="55">
@@ -4465,12 +4693,12 @@
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="54" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="90" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B19" s="90"/>
       <c r="C19" s="57">
@@ -4478,12 +4706,12 @@
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="54" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="90" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B20" s="90"/>
       <c r="C20" s="59">
@@ -4491,12 +4719,12 @@
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="54" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="90" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="73">
@@ -4504,12 +4732,12 @@
       </c>
       <c r="D21" s="44"/>
       <c r="E21" s="54" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="90" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B22" s="90"/>
       <c r="C22" s="73">
@@ -4517,7 +4745,7 @@
       </c>
       <c r="D22" s="44"/>
       <c r="E22" s="54" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4558,7 +4786,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4569,7 +4797,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4578,7 +4806,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4587,19 +4815,19 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4607,16 +4835,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="92" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4624,16 +4852,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4641,16 +4869,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="92" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4658,16 +4886,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="93" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4675,16 +4903,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="92" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4692,16 +4920,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="93" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4709,16 +4937,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="92" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4726,20 +4954,71 @@
         <v>8</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>215</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="53">
+        <v>9</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="63">
+        <v>10</v>
+      </c>
+      <c r="B14" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="53">
+        <v>11</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E12"/>
+  <autoFilter ref="A4:E15"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
